--- a/task_3/assignment_01.xlsx
+++ b/task_3/assignment_01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="237">
   <si>
     <t>product_name</t>
   </si>
@@ -65,6 +65,39 @@
   </si>
   <si>
     <t>cost_usd</t>
+  </si>
+  <si>
+    <t>judge_Fluency</t>
+  </si>
+  <si>
+    <t>judge_Grammar</t>
+  </si>
+  <si>
+    <t>judge_Tone</t>
+  </si>
+  <si>
+    <t>judge_Length</t>
+  </si>
+  <si>
+    <t>judge_Grounding</t>
+  </si>
+  <si>
+    <t>judge_final_score</t>
+  </si>
+  <si>
+    <t>isolated_Fluency</t>
+  </si>
+  <si>
+    <t>isolated_Grammar</t>
+  </si>
+  <si>
+    <t>isolated_Tone</t>
+  </si>
+  <si>
+    <t>isolated_Length</t>
+  </si>
+  <si>
+    <t>isolated_Grounding</t>
   </si>
   <si>
     <t>Apple iPhone 15 Pro</t>
@@ -687,6 +720,12 @@
   </si>
   <si>
     <t>pass</t>
+  </si>
+  <si>
+    <t>bad</t>
+  </si>
+  <si>
+    <t>fail</t>
   </si>
 </sst>
 </file>
@@ -1044,10 +1083,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:AB51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1099,22 +1138,55 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="F2">
         <v>1454.7</v>
@@ -1126,48 +1198,81 @@
         <v>98</v>
       </c>
       <c r="I2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="P2" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Q2">
         <v>8.02E-05</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" t="s">
+        <v>232</v>
+      </c>
+      <c r="S2" t="s">
+        <v>232</v>
+      </c>
+      <c r="T2" t="s">
+        <v>232</v>
+      </c>
+      <c r="U2" t="s">
+        <v>232</v>
+      </c>
+      <c r="V2" t="s">
+        <v>232</v>
+      </c>
+      <c r="W2" t="s">
+        <v>234</v>
+      </c>
+      <c r="X2" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="F3">
         <v>1058.3</v>
@@ -1181,22 +1286,55 @@
       <c r="Q3">
         <v>8.24E-05</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" t="s">
+        <v>232</v>
+      </c>
+      <c r="S3" t="s">
+        <v>232</v>
+      </c>
+      <c r="T3" t="s">
+        <v>232</v>
+      </c>
+      <c r="U3" t="s">
+        <v>232</v>
+      </c>
+      <c r="V3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W3" t="s">
+        <v>234</v>
+      </c>
+      <c r="X3" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>232</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E4" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="F4">
         <v>937.5</v>
@@ -1210,22 +1348,55 @@
       <c r="Q4">
         <v>7.92E-05</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" t="s">
+        <v>232</v>
+      </c>
+      <c r="S4" t="s">
+        <v>232</v>
+      </c>
+      <c r="T4" t="s">
+        <v>232</v>
+      </c>
+      <c r="U4" t="s">
+        <v>232</v>
+      </c>
+      <c r="V4" t="s">
+        <v>232</v>
+      </c>
+      <c r="W4" t="s">
+        <v>234</v>
+      </c>
+      <c r="X4" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E5" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="F5">
         <v>957.5</v>
@@ -1237,48 +1408,81 @@
         <v>95</v>
       </c>
       <c r="I5" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J5" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K5" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L5" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M5" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N5" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O5" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="P5" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Q5">
         <v>7.9E-05</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" t="s">
+        <v>232</v>
+      </c>
+      <c r="S5" t="s">
+        <v>232</v>
+      </c>
+      <c r="T5" t="s">
+        <v>232</v>
+      </c>
+      <c r="U5" t="s">
+        <v>232</v>
+      </c>
+      <c r="V5" t="s">
+        <v>233</v>
+      </c>
+      <c r="W5" t="s">
+        <v>234</v>
+      </c>
+      <c r="X5" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E6" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="F6">
         <v>828.4</v>
@@ -1292,22 +1496,55 @@
       <c r="Q6">
         <v>7.76E-05</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" t="s">
+        <v>232</v>
+      </c>
+      <c r="S6" t="s">
+        <v>232</v>
+      </c>
+      <c r="T6" t="s">
+        <v>232</v>
+      </c>
+      <c r="U6" t="s">
+        <v>232</v>
+      </c>
+      <c r="V6" t="s">
+        <v>232</v>
+      </c>
+      <c r="W6" t="s">
+        <v>234</v>
+      </c>
+      <c r="X6" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E7" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="F7">
         <v>2047.9</v>
@@ -1321,22 +1558,55 @@
       <c r="Q7">
         <v>7.640000000000001E-05</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" t="s">
+        <v>232</v>
+      </c>
+      <c r="S7" t="s">
+        <v>232</v>
+      </c>
+      <c r="T7" t="s">
+        <v>232</v>
+      </c>
+      <c r="U7" t="s">
+        <v>232</v>
+      </c>
+      <c r="V7" t="s">
+        <v>232</v>
+      </c>
+      <c r="W7" t="s">
+        <v>234</v>
+      </c>
+      <c r="X7" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="E8" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="F8">
         <v>1331.8</v>
@@ -1350,22 +1620,55 @@
       <c r="Q8">
         <v>8.619999999999999E-05</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" t="s">
+        <v>232</v>
+      </c>
+      <c r="S8" t="s">
+        <v>232</v>
+      </c>
+      <c r="T8" t="s">
+        <v>232</v>
+      </c>
+      <c r="U8" t="s">
+        <v>232</v>
+      </c>
+      <c r="V8" t="s">
+        <v>232</v>
+      </c>
+      <c r="W8" t="s">
+        <v>234</v>
+      </c>
+      <c r="X8" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E9" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="F9">
         <v>920.7</v>
@@ -1377,48 +1680,81 @@
         <v>99</v>
       </c>
       <c r="I9" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J9" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K9" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L9" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M9" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="N9" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O9" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="P9" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Q9">
         <v>8.04E-05</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" t="s">
+        <v>232</v>
+      </c>
+      <c r="S9" t="s">
+        <v>232</v>
+      </c>
+      <c r="T9" t="s">
+        <v>232</v>
+      </c>
+      <c r="U9" t="s">
+        <v>232</v>
+      </c>
+      <c r="V9" t="s">
+        <v>232</v>
+      </c>
+      <c r="W9" t="s">
+        <v>234</v>
+      </c>
+      <c r="X9" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E10" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="F10">
         <v>716.9</v>
@@ -1432,22 +1768,55 @@
       <c r="Q10">
         <v>7.36E-05</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" t="s">
+        <v>232</v>
+      </c>
+      <c r="S10" t="s">
+        <v>232</v>
+      </c>
+      <c r="T10" t="s">
+        <v>232</v>
+      </c>
+      <c r="U10" t="s">
+        <v>232</v>
+      </c>
+      <c r="V10" t="s">
+        <v>232</v>
+      </c>
+      <c r="W10" t="s">
+        <v>234</v>
+      </c>
+      <c r="X10" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E11" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="F11">
         <v>943.5</v>
@@ -1461,22 +1830,55 @@
       <c r="Q11">
         <v>8.26E-05</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" t="s">
+        <v>232</v>
+      </c>
+      <c r="S11" t="s">
+        <v>232</v>
+      </c>
+      <c r="T11" t="s">
+        <v>232</v>
+      </c>
+      <c r="U11" t="s">
+        <v>232</v>
+      </c>
+      <c r="V11" t="s">
+        <v>232</v>
+      </c>
+      <c r="W11" t="s">
+        <v>234</v>
+      </c>
+      <c r="X11" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E12" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="F12">
         <v>897.5</v>
@@ -1488,48 +1890,81 @@
         <v>98</v>
       </c>
       <c r="I12" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J12" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K12" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L12" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M12" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N12" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O12" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="P12" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Q12">
         <v>7.8E-05</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" t="s">
+        <v>232</v>
+      </c>
+      <c r="S12" t="s">
+        <v>232</v>
+      </c>
+      <c r="T12" t="s">
+        <v>232</v>
+      </c>
+      <c r="U12" t="s">
+        <v>232</v>
+      </c>
+      <c r="V12" t="s">
+        <v>232</v>
+      </c>
+      <c r="W12" t="s">
+        <v>234</v>
+      </c>
+      <c r="X12" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D13" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E13" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="F13">
         <v>1023.2</v>
@@ -1543,22 +1978,55 @@
       <c r="Q13">
         <v>8.3E-05</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13" t="s">
+        <v>232</v>
+      </c>
+      <c r="S13" t="s">
+        <v>232</v>
+      </c>
+      <c r="T13" t="s">
+        <v>232</v>
+      </c>
+      <c r="U13" t="s">
+        <v>232</v>
+      </c>
+      <c r="V13" t="s">
+        <v>232</v>
+      </c>
+      <c r="W13" t="s">
+        <v>234</v>
+      </c>
+      <c r="X13" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="D14" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E14" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F14">
         <v>1616.2</v>
@@ -1572,22 +2040,55 @@
       <c r="Q14">
         <v>8.000000000000001E-05</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14" t="s">
+        <v>232</v>
+      </c>
+      <c r="S14" t="s">
+        <v>232</v>
+      </c>
+      <c r="T14" t="s">
+        <v>232</v>
+      </c>
+      <c r="U14" t="s">
+        <v>232</v>
+      </c>
+      <c r="V14" t="s">
+        <v>232</v>
+      </c>
+      <c r="W14" t="s">
+        <v>234</v>
+      </c>
+      <c r="X14" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E15" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="F15">
         <v>878.5</v>
@@ -1601,22 +2102,55 @@
       <c r="Q15">
         <v>7.6E-05</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15" t="s">
+        <v>232</v>
+      </c>
+      <c r="S15" t="s">
+        <v>232</v>
+      </c>
+      <c r="T15" t="s">
+        <v>232</v>
+      </c>
+      <c r="U15" t="s">
+        <v>232</v>
+      </c>
+      <c r="V15" t="s">
+        <v>232</v>
+      </c>
+      <c r="W15" t="s">
+        <v>234</v>
+      </c>
+      <c r="X15" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="D16" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E16" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="F16">
         <v>1006.5</v>
@@ -1628,48 +2162,81 @@
         <v>103</v>
       </c>
       <c r="I16" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J16" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K16" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L16" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M16" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N16" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O16" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="P16" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Q16">
         <v>7.88E-05</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" t="s">
+        <v>232</v>
+      </c>
+      <c r="S16" t="s">
+        <v>232</v>
+      </c>
+      <c r="T16" t="s">
+        <v>232</v>
+      </c>
+      <c r="U16" t="s">
+        <v>232</v>
+      </c>
+      <c r="V16" t="s">
+        <v>232</v>
+      </c>
+      <c r="W16" t="s">
+        <v>234</v>
+      </c>
+      <c r="X16" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="D17" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E17" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="F17">
         <v>893</v>
@@ -1683,22 +2250,55 @@
       <c r="Q17">
         <v>8.000000000000001E-05</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" t="s">
+        <v>232</v>
+      </c>
+      <c r="S17" t="s">
+        <v>232</v>
+      </c>
+      <c r="T17" t="s">
+        <v>232</v>
+      </c>
+      <c r="U17" t="s">
+        <v>232</v>
+      </c>
+      <c r="V17" t="s">
+        <v>232</v>
+      </c>
+      <c r="W17" t="s">
+        <v>234</v>
+      </c>
+      <c r="X17" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D18" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E18" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="F18">
         <v>1660.6</v>
@@ -1712,22 +2312,55 @@
       <c r="Q18">
         <v>8.64E-05</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" t="s">
+        <v>232</v>
+      </c>
+      <c r="S18" t="s">
+        <v>232</v>
+      </c>
+      <c r="T18" t="s">
+        <v>232</v>
+      </c>
+      <c r="U18" t="s">
+        <v>232</v>
+      </c>
+      <c r="V18" t="s">
+        <v>232</v>
+      </c>
+      <c r="W18" t="s">
+        <v>234</v>
+      </c>
+      <c r="X18" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="D19" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E19" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="F19">
         <v>804</v>
@@ -1739,48 +2372,81 @@
         <v>83</v>
       </c>
       <c r="I19" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J19" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K19" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L19" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M19" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N19" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O19" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="P19" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Q19">
         <v>7.54E-05</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" t="s">
+        <v>232</v>
+      </c>
+      <c r="S19" t="s">
+        <v>232</v>
+      </c>
+      <c r="T19" t="s">
+        <v>232</v>
+      </c>
+      <c r="U19" t="s">
+        <v>232</v>
+      </c>
+      <c r="V19" t="s">
+        <v>232</v>
+      </c>
+      <c r="W19" t="s">
+        <v>234</v>
+      </c>
+      <c r="X19" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="E20" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="F20">
         <v>1130.7</v>
@@ -1794,22 +2460,55 @@
       <c r="Q20">
         <v>8.24E-05</v>
       </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20" t="s">
+        <v>232</v>
+      </c>
+      <c r="S20" t="s">
+        <v>232</v>
+      </c>
+      <c r="T20" t="s">
+        <v>232</v>
+      </c>
+      <c r="U20" t="s">
+        <v>232</v>
+      </c>
+      <c r="V20" t="s">
+        <v>233</v>
+      </c>
+      <c r="W20" t="s">
+        <v>234</v>
+      </c>
+      <c r="X20" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="E21" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="F21">
         <v>1015.6</v>
@@ -1823,22 +2522,55 @@
       <c r="Q21">
         <v>8.14E-05</v>
       </c>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21" t="s">
+        <v>232</v>
+      </c>
+      <c r="S21" t="s">
+        <v>232</v>
+      </c>
+      <c r="T21" t="s">
+        <v>232</v>
+      </c>
+      <c r="U21" t="s">
+        <v>233</v>
+      </c>
+      <c r="V21" t="s">
+        <v>232</v>
+      </c>
+      <c r="W21" t="s">
+        <v>234</v>
+      </c>
+      <c r="X21" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="D22" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E22" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="F22">
         <v>820.2</v>
@@ -1852,22 +2584,55 @@
       <c r="Q22">
         <v>7.780000000000001E-05</v>
       </c>
-    </row>
-    <row r="23" spans="1:17">
+      <c r="R22" t="s">
+        <v>232</v>
+      </c>
+      <c r="S22" t="s">
+        <v>232</v>
+      </c>
+      <c r="T22" t="s">
+        <v>232</v>
+      </c>
+      <c r="U22" t="s">
+        <v>232</v>
+      </c>
+      <c r="V22" t="s">
+        <v>232</v>
+      </c>
+      <c r="W22" t="s">
+        <v>234</v>
+      </c>
+      <c r="X22" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D23" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="E23" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="F23">
         <v>856.7</v>
@@ -1879,48 +2644,81 @@
         <v>93</v>
       </c>
       <c r="I23" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J23" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K23" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L23" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M23" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O23" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="P23" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Q23">
         <v>7.720000000000001E-05</v>
       </c>
-    </row>
-    <row r="24" spans="1:17">
+      <c r="R23" t="s">
+        <v>232</v>
+      </c>
+      <c r="S23" t="s">
+        <v>232</v>
+      </c>
+      <c r="T23" t="s">
+        <v>232</v>
+      </c>
+      <c r="U23" t="s">
+        <v>232</v>
+      </c>
+      <c r="V23" t="s">
+        <v>232</v>
+      </c>
+      <c r="W23" t="s">
+        <v>234</v>
+      </c>
+      <c r="X23" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D24" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="E24" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F24">
         <v>1088.1</v>
@@ -1934,22 +2732,55 @@
       <c r="Q24">
         <v>8.120000000000001E-05</v>
       </c>
-    </row>
-    <row r="25" spans="1:17">
+      <c r="R24" t="s">
+        <v>233</v>
+      </c>
+      <c r="S24" t="s">
+        <v>233</v>
+      </c>
+      <c r="T24" t="s">
+        <v>233</v>
+      </c>
+      <c r="U24" t="s">
+        <v>235</v>
+      </c>
+      <c r="V24" t="s">
+        <v>235</v>
+      </c>
+      <c r="W24" t="s">
+        <v>236</v>
+      </c>
+      <c r="X24" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="E25" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="F25">
         <v>823.9</v>
@@ -1963,22 +2794,55 @@
       <c r="Q25">
         <v>7.680000000000001E-05</v>
       </c>
-    </row>
-    <row r="26" spans="1:17">
+      <c r="R25" t="s">
+        <v>233</v>
+      </c>
+      <c r="S25" t="s">
+        <v>232</v>
+      </c>
+      <c r="T25" t="s">
+        <v>233</v>
+      </c>
+      <c r="U25" t="s">
+        <v>232</v>
+      </c>
+      <c r="V25" t="s">
+        <v>233</v>
+      </c>
+      <c r="W25" t="s">
+        <v>234</v>
+      </c>
+      <c r="X25" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D26" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="E26" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="F26">
         <v>797.2</v>
@@ -1990,48 +2854,81 @@
         <v>90</v>
       </c>
       <c r="I26" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J26" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K26" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="L26" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N26" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O26" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="P26" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Q26">
         <v>7.600000000000002E-05</v>
       </c>
-    </row>
-    <row r="27" spans="1:17">
+      <c r="R26" t="s">
+        <v>232</v>
+      </c>
+      <c r="S26" t="s">
+        <v>232</v>
+      </c>
+      <c r="T26" t="s">
+        <v>232</v>
+      </c>
+      <c r="U26" t="s">
+        <v>232</v>
+      </c>
+      <c r="V26" t="s">
+        <v>232</v>
+      </c>
+      <c r="W26" t="s">
+        <v>234</v>
+      </c>
+      <c r="X26" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="D27" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="E27" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="F27">
         <v>803.5</v>
@@ -2045,22 +2942,55 @@
       <c r="Q27">
         <v>7.660000000000001E-05</v>
       </c>
-    </row>
-    <row r="28" spans="1:17">
+      <c r="R27" t="s">
+        <v>232</v>
+      </c>
+      <c r="S27" t="s">
+        <v>232</v>
+      </c>
+      <c r="T27" t="s">
+        <v>232</v>
+      </c>
+      <c r="U27" t="s">
+        <v>232</v>
+      </c>
+      <c r="V27" t="s">
+        <v>232</v>
+      </c>
+      <c r="W27" t="s">
+        <v>234</v>
+      </c>
+      <c r="X27" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="D28" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="E28" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="F28">
         <v>867.5</v>
@@ -2074,22 +3004,55 @@
       <c r="Q28">
         <v>7.780000000000001E-05</v>
       </c>
-    </row>
-    <row r="29" spans="1:17">
+      <c r="R28" t="s">
+        <v>232</v>
+      </c>
+      <c r="S28" t="s">
+        <v>232</v>
+      </c>
+      <c r="T28" t="s">
+        <v>232</v>
+      </c>
+      <c r="U28" t="s">
+        <v>232</v>
+      </c>
+      <c r="V28" t="s">
+        <v>233</v>
+      </c>
+      <c r="W28" t="s">
+        <v>234</v>
+      </c>
+      <c r="X28" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="D29" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="E29" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="F29">
         <v>1006.2</v>
@@ -2103,22 +3066,55 @@
       <c r="Q29">
         <v>7.840000000000001E-05</v>
       </c>
-    </row>
-    <row r="30" spans="1:17">
+      <c r="R29" t="s">
+        <v>232</v>
+      </c>
+      <c r="S29" t="s">
+        <v>232</v>
+      </c>
+      <c r="T29" t="s">
+        <v>232</v>
+      </c>
+      <c r="U29" t="s">
+        <v>232</v>
+      </c>
+      <c r="V29" t="s">
+        <v>232</v>
+      </c>
+      <c r="W29" t="s">
+        <v>234</v>
+      </c>
+      <c r="X29" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D30" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="E30" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F30">
         <v>945.8</v>
@@ -2130,48 +3126,81 @@
         <v>112</v>
       </c>
       <c r="I30" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J30" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K30" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L30" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M30" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N30" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O30" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="P30" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Q30">
         <v>8.1E-05</v>
       </c>
-    </row>
-    <row r="31" spans="1:17">
+      <c r="R30" t="s">
+        <v>232</v>
+      </c>
+      <c r="S30" t="s">
+        <v>232</v>
+      </c>
+      <c r="T30" t="s">
+        <v>232</v>
+      </c>
+      <c r="U30" t="s">
+        <v>232</v>
+      </c>
+      <c r="V30" t="s">
+        <v>232</v>
+      </c>
+      <c r="W30" t="s">
+        <v>234</v>
+      </c>
+      <c r="X30" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D31" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="E31" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="F31">
         <v>897.2</v>
@@ -2185,22 +3214,55 @@
       <c r="Q31">
         <v>7.46E-05</v>
       </c>
-    </row>
-    <row r="32" spans="1:17">
+      <c r="R31" t="s">
+        <v>232</v>
+      </c>
+      <c r="S31" t="s">
+        <v>232</v>
+      </c>
+      <c r="T31" t="s">
+        <v>232</v>
+      </c>
+      <c r="U31" t="s">
+        <v>232</v>
+      </c>
+      <c r="V31" t="s">
+        <v>232</v>
+      </c>
+      <c r="W31" t="s">
+        <v>234</v>
+      </c>
+      <c r="X31" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>232</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>232</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D32" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E32" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="F32">
         <v>898.9</v>
@@ -2214,22 +3276,55 @@
       <c r="Q32">
         <v>7.82E-05</v>
       </c>
-    </row>
-    <row r="33" spans="1:17">
+      <c r="R32" t="s">
+        <v>232</v>
+      </c>
+      <c r="S32" t="s">
+        <v>232</v>
+      </c>
+      <c r="T32" t="s">
+        <v>232</v>
+      </c>
+      <c r="U32" t="s">
+        <v>235</v>
+      </c>
+      <c r="V32" t="s">
+        <v>233</v>
+      </c>
+      <c r="W32" t="s">
+        <v>236</v>
+      </c>
+      <c r="X32" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D33" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E33" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="F33">
         <v>956.6</v>
@@ -2241,48 +3336,81 @@
         <v>96</v>
       </c>
       <c r="I33" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J33" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K33" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L33" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M33" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N33" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O33" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="P33" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Q33">
         <v>7.800000000000001E-05</v>
       </c>
-    </row>
-    <row r="34" spans="1:17">
+      <c r="R33" t="s">
+        <v>232</v>
+      </c>
+      <c r="S33" t="s">
+        <v>232</v>
+      </c>
+      <c r="T33" t="s">
+        <v>232</v>
+      </c>
+      <c r="U33" t="s">
+        <v>232</v>
+      </c>
+      <c r="V33" t="s">
+        <v>233</v>
+      </c>
+      <c r="W33" t="s">
+        <v>234</v>
+      </c>
+      <c r="X33" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C34" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D34" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E34" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="F34">
         <v>1010.7</v>
@@ -2296,22 +3424,55 @@
       <c r="Q34">
         <v>8.16E-05</v>
       </c>
-    </row>
-    <row r="35" spans="1:17">
+      <c r="R34" t="s">
+        <v>232</v>
+      </c>
+      <c r="S34" t="s">
+        <v>232</v>
+      </c>
+      <c r="T34" t="s">
+        <v>232</v>
+      </c>
+      <c r="U34" t="s">
+        <v>232</v>
+      </c>
+      <c r="V34" t="s">
+        <v>232</v>
+      </c>
+      <c r="W34" t="s">
+        <v>234</v>
+      </c>
+      <c r="X34" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="D35" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E35" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F35">
         <v>1108.1</v>
@@ -2325,22 +3486,55 @@
       <c r="Q35">
         <v>8.360000000000001E-05</v>
       </c>
-    </row>
-    <row r="36" spans="1:17">
+      <c r="R35" t="s">
+        <v>232</v>
+      </c>
+      <c r="S35" t="s">
+        <v>232</v>
+      </c>
+      <c r="T35" t="s">
+        <v>232</v>
+      </c>
+      <c r="U35" t="s">
+        <v>232</v>
+      </c>
+      <c r="V35" t="s">
+        <v>232</v>
+      </c>
+      <c r="W35" t="s">
+        <v>234</v>
+      </c>
+      <c r="X35" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>232</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C36" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="D36" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="E36" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="F36">
         <v>860.4</v>
@@ -2354,22 +3548,55 @@
       <c r="Q36">
         <v>7.580000000000001E-05</v>
       </c>
-    </row>
-    <row r="37" spans="1:17">
+      <c r="R36" t="s">
+        <v>232</v>
+      </c>
+      <c r="S36" t="s">
+        <v>232</v>
+      </c>
+      <c r="T36" t="s">
+        <v>232</v>
+      </c>
+      <c r="U36" t="s">
+        <v>232</v>
+      </c>
+      <c r="V36" t="s">
+        <v>232</v>
+      </c>
+      <c r="W36" t="s">
+        <v>234</v>
+      </c>
+      <c r="X36" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C37" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D37" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E37" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="F37">
         <v>998.3</v>
@@ -2381,48 +3608,81 @@
         <v>110</v>
       </c>
       <c r="I37" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J37" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K37" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L37" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M37" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N37" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O37" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="P37" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Q37">
         <v>8.14E-05</v>
       </c>
-    </row>
-    <row r="38" spans="1:17">
+      <c r="R37" t="s">
+        <v>232</v>
+      </c>
+      <c r="S37" t="s">
+        <v>232</v>
+      </c>
+      <c r="T37" t="s">
+        <v>232</v>
+      </c>
+      <c r="U37" t="s">
+        <v>232</v>
+      </c>
+      <c r="V37" t="s">
+        <v>232</v>
+      </c>
+      <c r="W37" t="s">
+        <v>234</v>
+      </c>
+      <c r="X37" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C38" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D38" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="E38" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="F38">
         <v>1127</v>
@@ -2436,22 +3696,55 @@
       <c r="Q38">
         <v>7.600000000000002E-05</v>
       </c>
-    </row>
-    <row r="39" spans="1:17">
+      <c r="R38" t="s">
+        <v>232</v>
+      </c>
+      <c r="S38" t="s">
+        <v>232</v>
+      </c>
+      <c r="T38" t="s">
+        <v>232</v>
+      </c>
+      <c r="U38" t="s">
+        <v>232</v>
+      </c>
+      <c r="V38" t="s">
+        <v>233</v>
+      </c>
+      <c r="W38" t="s">
+        <v>234</v>
+      </c>
+      <c r="X38" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>235</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B39" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C39" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D39" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="E39" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="F39">
         <v>1225.2</v>
@@ -2465,22 +3758,55 @@
       <c r="Q39">
         <v>8.42E-05</v>
       </c>
-    </row>
-    <row r="40" spans="1:17">
+      <c r="R39" t="s">
+        <v>232</v>
+      </c>
+      <c r="S39" t="s">
+        <v>232</v>
+      </c>
+      <c r="T39" t="s">
+        <v>232</v>
+      </c>
+      <c r="U39" t="s">
+        <v>233</v>
+      </c>
+      <c r="V39" t="s">
+        <v>232</v>
+      </c>
+      <c r="W39" t="s">
+        <v>234</v>
+      </c>
+      <c r="X39" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="D40" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E40" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="F40">
         <v>924.1</v>
@@ -2492,48 +3818,81 @@
         <v>101</v>
       </c>
       <c r="I40" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J40" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K40" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L40" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M40" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N40" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O40" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="P40" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Q40">
         <v>7.839999999999999E-05</v>
       </c>
-    </row>
-    <row r="41" spans="1:17">
+      <c r="R40" t="s">
+        <v>232</v>
+      </c>
+      <c r="S40" t="s">
+        <v>232</v>
+      </c>
+      <c r="T40" t="s">
+        <v>232</v>
+      </c>
+      <c r="U40" t="s">
+        <v>232</v>
+      </c>
+      <c r="V40" t="s">
+        <v>232</v>
+      </c>
+      <c r="W40" t="s">
+        <v>234</v>
+      </c>
+      <c r="X40" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>235</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C41" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D41" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E41" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="F41">
         <v>817.9</v>
@@ -2547,22 +3906,55 @@
       <c r="Q41">
         <v>7.46E-05</v>
       </c>
-    </row>
-    <row r="42" spans="1:17">
+      <c r="R41" t="s">
+        <v>232</v>
+      </c>
+      <c r="S41" t="s">
+        <v>232</v>
+      </c>
+      <c r="T41" t="s">
+        <v>232</v>
+      </c>
+      <c r="U41" t="s">
+        <v>232</v>
+      </c>
+      <c r="V41" t="s">
+        <v>232</v>
+      </c>
+      <c r="W41" t="s">
+        <v>234</v>
+      </c>
+      <c r="X41" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B42" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D42" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="E42" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="F42">
         <v>905.9</v>
@@ -2576,22 +3968,55 @@
       <c r="Q42">
         <v>7.88E-05</v>
       </c>
-    </row>
-    <row r="43" spans="1:17">
+      <c r="R42" t="s">
+        <v>232</v>
+      </c>
+      <c r="S42" t="s">
+        <v>232</v>
+      </c>
+      <c r="T42" t="s">
+        <v>232</v>
+      </c>
+      <c r="U42" t="s">
+        <v>232</v>
+      </c>
+      <c r="V42" t="s">
+        <v>232</v>
+      </c>
+      <c r="W42" t="s">
+        <v>234</v>
+      </c>
+      <c r="X42" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C43" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D43" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E43" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="F43">
         <v>1036.6</v>
@@ -2605,22 +4030,55 @@
       <c r="Q43">
         <v>7.539999999999999E-05</v>
       </c>
-    </row>
-    <row r="44" spans="1:17">
+      <c r="R43" t="s">
+        <v>232</v>
+      </c>
+      <c r="S43" t="s">
+        <v>232</v>
+      </c>
+      <c r="T43" t="s">
+        <v>232</v>
+      </c>
+      <c r="U43" t="s">
+        <v>232</v>
+      </c>
+      <c r="V43" t="s">
+        <v>232</v>
+      </c>
+      <c r="W43" t="s">
+        <v>234</v>
+      </c>
+      <c r="X43" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>232</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C44" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D44" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="E44" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="F44">
         <v>906.7</v>
@@ -2632,48 +4090,81 @@
         <v>109</v>
       </c>
       <c r="I44" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J44" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K44" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L44" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M44" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="N44" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O44" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="P44" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Q44">
         <v>8.060000000000001E-05</v>
       </c>
-    </row>
-    <row r="45" spans="1:17">
+      <c r="R44" t="s">
+        <v>232</v>
+      </c>
+      <c r="S44" t="s">
+        <v>232</v>
+      </c>
+      <c r="T44" t="s">
+        <v>232</v>
+      </c>
+      <c r="U44" t="s">
+        <v>235</v>
+      </c>
+      <c r="V44" t="s">
+        <v>232</v>
+      </c>
+      <c r="W44" t="s">
+        <v>236</v>
+      </c>
+      <c r="X44" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>235</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B45" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C45" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="D45" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="E45" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="F45">
         <v>1347.2</v>
@@ -2687,22 +4178,55 @@
       <c r="Q45">
         <v>8.440000000000001E-05</v>
       </c>
-    </row>
-    <row r="46" spans="1:17">
+      <c r="R45" t="s">
+        <v>232</v>
+      </c>
+      <c r="S45" t="s">
+        <v>232</v>
+      </c>
+      <c r="T45" t="s">
+        <v>232</v>
+      </c>
+      <c r="U45" t="s">
+        <v>232</v>
+      </c>
+      <c r="V45" t="s">
+        <v>232</v>
+      </c>
+      <c r="W45" t="s">
+        <v>234</v>
+      </c>
+      <c r="X45" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>232</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B46" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="C46" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="D46" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E46" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="F46">
         <v>1848.6</v>
@@ -2716,22 +4240,55 @@
       <c r="Q46">
         <v>8.460000000000001E-05</v>
       </c>
-    </row>
-    <row r="47" spans="1:17">
+      <c r="R46" t="s">
+        <v>232</v>
+      </c>
+      <c r="S46" t="s">
+        <v>232</v>
+      </c>
+      <c r="T46" t="s">
+        <v>232</v>
+      </c>
+      <c r="U46" t="s">
+        <v>232</v>
+      </c>
+      <c r="V46" t="s">
+        <v>232</v>
+      </c>
+      <c r="W46" t="s">
+        <v>234</v>
+      </c>
+      <c r="X46" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C47" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D47" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E47" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F47">
         <v>909</v>
@@ -2743,48 +4300,81 @@
         <v>99</v>
       </c>
       <c r="I47" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J47" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K47" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L47" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M47" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N47" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O47" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="P47" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Q47">
         <v>7.980000000000002E-05</v>
       </c>
-    </row>
-    <row r="48" spans="1:17">
+      <c r="R47" t="s">
+        <v>232</v>
+      </c>
+      <c r="S47" t="s">
+        <v>232</v>
+      </c>
+      <c r="T47" t="s">
+        <v>232</v>
+      </c>
+      <c r="U47" t="s">
+        <v>232</v>
+      </c>
+      <c r="V47" t="s">
+        <v>232</v>
+      </c>
+      <c r="W47" t="s">
+        <v>234</v>
+      </c>
+      <c r="X47" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B48" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="C48" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="D48" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="E48" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="F48">
         <v>991.2</v>
@@ -2798,22 +4388,55 @@
       <c r="Q48">
         <v>8.3E-05</v>
       </c>
-    </row>
-    <row r="49" spans="1:17">
+      <c r="R48" t="s">
+        <v>232</v>
+      </c>
+      <c r="S48" t="s">
+        <v>232</v>
+      </c>
+      <c r="T48" t="s">
+        <v>232</v>
+      </c>
+      <c r="U48" t="s">
+        <v>235</v>
+      </c>
+      <c r="V48" t="s">
+        <v>233</v>
+      </c>
+      <c r="W48" t="s">
+        <v>236</v>
+      </c>
+      <c r="X48" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B49" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C49" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D49" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E49" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="F49">
         <v>971.5</v>
@@ -2827,22 +4450,55 @@
       <c r="Q49">
         <v>8.26E-05</v>
       </c>
-    </row>
-    <row r="50" spans="1:17">
+      <c r="R49" t="s">
+        <v>232</v>
+      </c>
+      <c r="S49" t="s">
+        <v>232</v>
+      </c>
+      <c r="T49" t="s">
+        <v>232</v>
+      </c>
+      <c r="U49" t="s">
+        <v>232</v>
+      </c>
+      <c r="V49" t="s">
+        <v>232</v>
+      </c>
+      <c r="W49" t="s">
+        <v>234</v>
+      </c>
+      <c r="X49" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B50" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C50" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="D50" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E50" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="F50">
         <v>1111.5</v>
@@ -2856,22 +4512,55 @@
       <c r="Q50">
         <v>7.980000000000002E-05</v>
       </c>
-    </row>
-    <row r="51" spans="1:17">
+      <c r="R50" t="s">
+        <v>232</v>
+      </c>
+      <c r="S50" t="s">
+        <v>232</v>
+      </c>
+      <c r="T50" t="s">
+        <v>232</v>
+      </c>
+      <c r="U50" t="s">
+        <v>232</v>
+      </c>
+      <c r="V50" t="s">
+        <v>232</v>
+      </c>
+      <c r="W50" t="s">
+        <v>234</v>
+      </c>
+      <c r="X50" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B51" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="C51" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="D51" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E51" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F51">
         <v>1178.6</v>
@@ -2883,31 +4572,64 @@
         <v>106</v>
       </c>
       <c r="I51" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J51" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K51" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L51" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M51" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N51" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O51" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="P51" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Q51">
         <v>8.26E-05</v>
+      </c>
+      <c r="R51" t="s">
+        <v>232</v>
+      </c>
+      <c r="S51" t="s">
+        <v>232</v>
+      </c>
+      <c r="T51" t="s">
+        <v>232</v>
+      </c>
+      <c r="U51" t="s">
+        <v>232</v>
+      </c>
+      <c r="V51" t="s">
+        <v>232</v>
+      </c>
+      <c r="W51" t="s">
+        <v>234</v>
+      </c>
+      <c r="X51" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
